--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -592,9 +592,7 @@
       <c r="G5" s="1" t="n">
         <v>99.3</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +546,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>24129.75</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>-88.25</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>24219.5</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>24255</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>24106</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>42436</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>08:14 CT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,6 +610,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>584.98</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>573.97</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>586.05</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>571.92</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>50941699</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>04/02/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,6 +674,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>66846.52</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-87.19</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>66885.28999999999</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>67245.84</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>66321.34</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>164679792</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>04/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -598,6 +736,37 @@
           <t>17:39 ET</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>100.03</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>04/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,6 +800,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.8724499999999999</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.87243</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.87327</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.87174</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>162556</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>16:00 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -664,6 +864,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5527</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>247178</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>16:00 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,6 +928,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.39465</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.39208</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.39495</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.39157</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>123017</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -730,6 +992,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.96154</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>-0.00049</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.96201</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.96266</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.9595900000000001</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>140679</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -763,6 +1056,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -796,6 +1120,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -829,6 +1184,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>72.988</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>73.014</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>73.014</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>72.98699999999999</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>1513</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -862,6 +1248,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4676.4</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4676.63</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4676.63</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4676.4</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>846</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>06:09 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -895,6 +1312,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5738</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>64969</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -928,6 +1376,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.60625</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.60624</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.60829</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.60535</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>143621</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -961,6 +1440,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>159.67</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>159.596</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>159.806</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>159.434</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>205815</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -994,6 +1504,37 @@
           <t>04/01/26</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.92143</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>-0.00033</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.92176</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.92265</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.92089</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>169062</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1025,6 +1566,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>04/01/26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.80008</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0.00124</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.79883</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.80126</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.79771</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>130514</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -759,9 +759,7 @@
       <c r="R5" s="1" t="n">
         <v>99.95</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>04/03/26</t>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1601,4 +1602,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>25074.25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>703.25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>24514</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>25257</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>24355</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>627124</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>606.09</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>608.71</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>609.9</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>602.12</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>62241594</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>71346.75999999999</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2019.33</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>71979.31</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>72631.85000000001</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>69327.42999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>330772127</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.8706199999999999</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00168</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.87229</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.87294</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86861</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>656614</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1014793</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.38461</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.00396</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.38856</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.3899</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.38235</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>415870</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.97525</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.9686900000000001</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.9801800000000001</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.96763</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>425174</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>74.09699999999999</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>72.98</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>77.637</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>72.959</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>186760</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4719.14</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4706.56</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4853.18</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4700.46</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>208039</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>326968</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.61471</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.61013</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.62306</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61004</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>503876</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>158.573</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-1.047</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>159.62</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.66</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>157.89</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>647528</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92291</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92508</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92613</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92064</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>544790</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.79138</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00637</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.79775</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.79872</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.78694</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>512700</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>04/08/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -1610,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1659,6 +1659,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1692,6 +1737,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>25281.25</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>25237</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>25393</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>25193</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>424036</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1725,6 +1801,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>611.0700000000001</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>611.84</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>613.67</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>609.58</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>33755973</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1758,6 +1865,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>73348.33</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1042.58</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>71760.99000000001</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>73392.8</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>71483.91</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>188349008</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1783,12 +1921,41 @@
       <c r="G5" s="1" t="n">
         <v>98.53</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>17:39 ET</t>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>04/10/26</t>
         </is>
       </c>
     </row>
@@ -1824,6 +1991,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.87096</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.00021</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.87076</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.87191</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.87035</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>414821</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1857,6 +2055,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5603</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>688255</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1890,6 +2119,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.3841</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.38157</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.38441</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.37993</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>257225</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1923,6 +2183,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>-0.00088</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.97868</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.97997</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.97644</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>277307</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1956,6 +2247,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1989,6 +2311,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2022,6 +2375,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>75.982</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>75.27800000000001</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>76.827</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>74.848</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>160241</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2055,6 +2439,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4748.7</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4765.42</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4794.75</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4731.58</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>174019</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2088,6 +2503,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>226721</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2121,6 +2567,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.62285</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.00652</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.61631</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.61554</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>340521</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2154,6 +2631,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>158.979</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>159.373</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>158.952</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>428319</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2187,6 +2695,37 @@
           <t>04/08/26</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.92533</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.92479</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.92608</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.92191</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>371230</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2218,6 +2757,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>04/08/26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.78914</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>-0.00136</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.79049</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.7914099999999999</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.78549</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>326644</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -1950,9 +1950,7 @@
       <c r="R5" s="1" t="n">
         <v>98.54000000000001</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>04/10/26</t>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2792,4 +2793,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>26365.5</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>25985.75</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>26377.5</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>25933.75</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>504457</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>629.08</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>637.83</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>628.2</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>49716531</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>73990.92</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-109.97</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>74100.89999999999</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>74722.19</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>73588.42</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>241916624</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>05:01 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.87002</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00057</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.8694499999999999</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.8701100000000001</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86871</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>456407</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>708516</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.3742</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.00247</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.37667</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.37882</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.3727</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>289404</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98534</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98103</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98547</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98017</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>271591</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>78.952</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-0.609</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>79.56100000000001</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>80.996</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>78.337</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>170534</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4790.73</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-50.75</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4841.5</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4871.02</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4788.19</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>184415</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5697</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>248141</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.6214</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00247</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.62387</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.62482</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61953</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>372741</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>158.973</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>158.788</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.154</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>158.648</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>471974</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92259</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00144</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92115</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92276</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91975</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>395780</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.7819199999999999</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00103</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.78088</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.78315</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.77988</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>366877</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -2974,9 +2974,7 @@
       <c r="G5" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3413,4 +3414,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>27083</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>448.25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>26729.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>27136</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>26727.75</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>498811</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>655.11</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>650.15</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>655.33</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>648.52</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>36624867</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>78450.87</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2716.64</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>75775.24000000001</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>79452.89</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>75318.42</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.37</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86687</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00246</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86934</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86998</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86672</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>436214</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>721487</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.36716</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00088</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.36627</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.36749</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.36435</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>276683</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.9789600000000001</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.97739</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.97939</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.97657</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>273971</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>77.727</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>76.702</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>78.67100000000001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>76.697</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>168482</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4740.28</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4720.23</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4771.85</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4715.77</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>169797</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>236197</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.60031</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00415</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60445</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.6059</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.59937</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>352630</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>159.483</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>159.383</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.573</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.105</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>475638</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.91862</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91689</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91605</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>363921</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00403</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.78078</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.77923</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>339553</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>04/22/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -3595,9 +3595,7 @@
       <c r="G5" s="1" t="n">
         <v>98.20999999999999</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4034,4 +4035,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>27325.25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>27197.25</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>27414</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>27094</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>511902</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>661.5700000000001</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>658.63</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>661.72</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>656.59</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>29957324</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>75626.88</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-853.11</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>76480</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>77857.10000000001</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>74916.16</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86635</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86643</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86739</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86617</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>477862</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>833317</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.36853</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.36824</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.37108</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.36675</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>323972</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.97377</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.008840000000000001</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98263</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98346</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.97235</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>323447</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>71.307</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>73.107</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>73.949</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>70.893</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>176225</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4543.68</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-53.39</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4597.07</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4609.91</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4510.55</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>200106</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5789</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>253780</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.5977</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00481</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60252</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.60294</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.59628</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>356394</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>160.439</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>159.618</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>160.467</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.522</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>413809</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92415</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00029</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92443</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92514</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.9230699999999999</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>403141</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.79157</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.7892400000000001</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.79248</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.78833</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>395766</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/april.xlsx
+++ b/outputs/april.xlsx
@@ -4216,9 +4216,7 @@
       <c r="G5" s="1" t="n">
         <v>98.56999999999999</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
